--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/188.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/188.xlsx
@@ -426,13 +426,13 @@
         <v>-3.2487433210856</v>
       </c>
       <c r="E2">
-        <v>-15.74467296216002</v>
+        <v>-15.92061776278004</v>
       </c>
       <c r="F2">
-        <v>1.860643964578226</v>
+        <v>0.8859046477435545</v>
       </c>
       <c r="G2">
-        <v>-8.455141079058023</v>
+        <v>-11.30243535992792</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.857311957269896</v>
       </c>
       <c r="E3">
-        <v>-16.29226962458955</v>
+        <v>-15.66675150991004</v>
       </c>
       <c r="F3">
-        <v>1.809091169618841</v>
+        <v>0.7512437174596538</v>
       </c>
       <c r="G3">
-        <v>-8.131316756588674</v>
+        <v>-10.89401004620249</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.533013227430146</v>
       </c>
       <c r="E4">
-        <v>-17.40932189348361</v>
+        <v>-15.09749062782782</v>
       </c>
       <c r="F4">
-        <v>1.605603963955857</v>
+        <v>1.172997272388502</v>
       </c>
       <c r="G4">
-        <v>-8.593028611314208</v>
+        <v>-9.811872162507681</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.314540269831933</v>
       </c>
       <c r="E5">
-        <v>-17.23114908365183</v>
+        <v>-17.40804939228746</v>
       </c>
       <c r="F5">
-        <v>2.022242148777836</v>
+        <v>1.222769981898933</v>
       </c>
       <c r="G5">
-        <v>-7.396941750157685</v>
+        <v>-9.883671274163396</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.174751870258167</v>
       </c>
       <c r="E6">
-        <v>-18.13750504239102</v>
+        <v>-17.98718687618041</v>
       </c>
       <c r="F6">
-        <v>1.906900846956381</v>
+        <v>1.004755441873623</v>
       </c>
       <c r="G6">
-        <v>-6.961148156459105</v>
+        <v>-9.974062409567654</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.10111941819852</v>
       </c>
       <c r="E7">
-        <v>-18.48350309894707</v>
+        <v>-19.20687700845833</v>
       </c>
       <c r="F7">
-        <v>2.143169181363046</v>
+        <v>1.09813866117751</v>
       </c>
       <c r="G7">
-        <v>-6.24737798546454</v>
+        <v>-8.835635320068619</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.066871619237419</v>
       </c>
       <c r="E8">
-        <v>-19.31592266256303</v>
+        <v>-20.03962715067684</v>
       </c>
       <c r="F8">
-        <v>2.141943392984496</v>
+        <v>1.266372573162812</v>
       </c>
       <c r="G8">
-        <v>-6.222462819735986</v>
+        <v>-9.268472596600629</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.054836774048034</v>
       </c>
       <c r="E9">
-        <v>-19.97490167168521</v>
+        <v>-19.55591819954753</v>
       </c>
       <c r="F9">
-        <v>2.39830103692851</v>
+        <v>1.007945025587318</v>
       </c>
       <c r="G9">
-        <v>-5.969676183448317</v>
+        <v>-7.981064336743311</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.045908451654815</v>
       </c>
       <c r="E10">
-        <v>-20.32655126380284</v>
+        <v>-20.32137068953806</v>
       </c>
       <c r="F10">
-        <v>2.504437839969431</v>
+        <v>1.604221388691678</v>
       </c>
       <c r="G10">
-        <v>-4.967683296713724</v>
+        <v>-8.881963094345179</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.031222196984838</v>
       </c>
       <c r="E11">
-        <v>-21.83586447971532</v>
+        <v>-21.43740858025441</v>
       </c>
       <c r="F11">
-        <v>2.762410863947193</v>
+        <v>1.926975903140491</v>
       </c>
       <c r="G11">
-        <v>-5.091785717344383</v>
+        <v>-7.794422400330281</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.01020232047531</v>
       </c>
       <c r="E12">
-        <v>-21.68367152526553</v>
+        <v>-22.031684752755</v>
       </c>
       <c r="F12">
-        <v>2.96461210040684</v>
+        <v>1.636581251661853</v>
       </c>
       <c r="G12">
-        <v>-4.4205262616196</v>
+        <v>-7.039906034838366</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.987813906506408</v>
       </c>
       <c r="E13">
-        <v>-22.06774499127808</v>
+        <v>-22.54448009243558</v>
       </c>
       <c r="F13">
-        <v>3.150208180343105</v>
+        <v>2.017928133864179</v>
       </c>
       <c r="G13">
-        <v>-3.77764480225745</v>
+        <v>-6.599586925387602</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.975243435507603</v>
       </c>
       <c r="E14">
-        <v>-24.53196393576599</v>
+        <v>-24.53674147584409</v>
       </c>
       <c r="F14">
-        <v>3.045110288382712</v>
+        <v>2.383928905745897</v>
       </c>
       <c r="G14">
-        <v>-4.147320180445706</v>
+        <v>-5.70533574322859</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.981619191041659</v>
       </c>
       <c r="E15">
-        <v>-24.94362939390727</v>
+        <v>-24.48394399738865</v>
       </c>
       <c r="F15">
-        <v>3.960186652265033</v>
+        <v>2.617441591859697</v>
       </c>
       <c r="G15">
-        <v>-3.589387319621255</v>
+        <v>-6.174135475953705</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.009801672594474</v>
       </c>
       <c r="E16">
-        <v>-25.45038827773562</v>
+        <v>-25.18492460293198</v>
       </c>
       <c r="F16">
-        <v>4.329161623855946</v>
+        <v>3.2945107122402</v>
       </c>
       <c r="G16">
-        <v>-3.188755030095273</v>
+        <v>-5.891414886899946</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.059916089897477</v>
       </c>
       <c r="E17">
-        <v>-27.02517869932501</v>
+        <v>-26.36155800434497</v>
       </c>
       <c r="F17">
-        <v>4.19736403386716</v>
+        <v>2.769395007034281</v>
       </c>
       <c r="G17">
-        <v>-2.634351210815685</v>
+        <v>-6.217513554154776</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.128911443437236</v>
       </c>
       <c r="E18">
-        <v>-28.31528660242221</v>
+        <v>-27.7512878071369</v>
       </c>
       <c r="F18">
-        <v>4.578124944880773</v>
+        <v>3.409318305168152</v>
       </c>
       <c r="G18">
-        <v>-3.72036574333698</v>
+        <v>-5.903412303934265</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.213291543784323</v>
       </c>
       <c r="E19">
-        <v>-28.79227076965013</v>
+        <v>-28.75969292763894</v>
       </c>
       <c r="F19">
-        <v>4.684233241215217</v>
+        <v>3.51184109131004</v>
       </c>
       <c r="G19">
-        <v>-2.387030285213352</v>
+        <v>-5.514837021262309</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.315099427673372</v>
       </c>
       <c r="E20">
-        <v>-28.74806833486126</v>
+        <v>-28.33656137331024</v>
       </c>
       <c r="F20">
-        <v>5.04023449394685</v>
+        <v>3.894638648130909</v>
       </c>
       <c r="G20">
-        <v>-2.952531053140578</v>
+        <v>-4.923027347934495</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.434204391345197</v>
       </c>
       <c r="E21">
-        <v>-29.5699727818314</v>
+        <v>-27.76471473256964</v>
       </c>
       <c r="F21">
-        <v>5.268169367826473</v>
+        <v>4.289323501553067</v>
       </c>
       <c r="G21">
-        <v>-2.781491717854132</v>
+        <v>-6.159900130134839</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.571936746963981</v>
       </c>
       <c r="E22">
-        <v>-30.30585660078885</v>
+        <v>-30.01692184520345</v>
       </c>
       <c r="F22">
-        <v>5.230917437283505</v>
+        <v>4.084919330165044</v>
       </c>
       <c r="G22">
-        <v>-2.382829202924017</v>
+        <v>-4.680983431921761</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.729540364965595</v>
       </c>
       <c r="E23">
-        <v>-30.3949180990977</v>
+        <v>-29.18459058683064</v>
       </c>
       <c r="F23">
-        <v>5.438756666802117</v>
+        <v>4.391966649344528</v>
       </c>
       <c r="G23">
-        <v>-2.744608930001112</v>
+        <v>-5.48921008824281</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.903063229406312</v>
       </c>
       <c r="E24">
-        <v>-31.45722111723904</v>
+        <v>-30.42318483385358</v>
       </c>
       <c r="F24">
-        <v>4.810825189859953</v>
+        <v>3.812295442763551</v>
       </c>
       <c r="G24">
-        <v>-2.447265661300391</v>
+        <v>-4.826419008007483</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.092931943917319</v>
       </c>
       <c r="E25">
-        <v>-29.58584055475428</v>
+        <v>-32.5443967788675</v>
       </c>
       <c r="F25">
-        <v>5.051995094074903</v>
+        <v>3.984501289184775</v>
       </c>
       <c r="G25">
-        <v>-2.705163779900695</v>
+        <v>-6.38065392778452</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.29540160625203</v>
       </c>
       <c r="E26">
-        <v>-30.95402840669172</v>
+        <v>-30.27498825771556</v>
       </c>
       <c r="F26">
-        <v>5.021787487443811</v>
+        <v>4.129283683974249</v>
       </c>
       <c r="G26">
-        <v>-3.081109331340331</v>
+        <v>-5.424310153490938</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.506445328973433</v>
       </c>
       <c r="E27">
-        <v>-31.02210042797503</v>
+        <v>-29.96744826666965</v>
       </c>
       <c r="F27">
-        <v>4.661446880503874</v>
+        <v>3.633240068258051</v>
       </c>
       <c r="G27">
-        <v>-2.456624573539911</v>
+        <v>-5.33613708359799</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.725843737809649</v>
       </c>
       <c r="E28">
-        <v>-30.39641023128323</v>
+        <v>-29.90942945768338</v>
       </c>
       <c r="F28">
-        <v>4.947510096303786</v>
+        <v>3.511882267663842</v>
       </c>
       <c r="G28">
-        <v>-1.786980664038292</v>
+        <v>-5.94739952251456</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.948536980049439</v>
       </c>
       <c r="E29">
-        <v>-30.56527023431824</v>
+        <v>-29.65739497254948</v>
       </c>
       <c r="F29">
-        <v>4.554313926442141</v>
+        <v>4.141430708345669</v>
       </c>
       <c r="G29">
-        <v>-2.410617922180659</v>
+        <v>-5.782852167030626</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.173867513955814</v>
       </c>
       <c r="E30">
-        <v>-29.4154114354756</v>
+        <v>-30.93412123495401</v>
       </c>
       <c r="F30">
-        <v>4.488623388775628</v>
+        <v>3.737959454504654</v>
       </c>
       <c r="G30">
-        <v>-2.014090709123374</v>
+        <v>-5.234797974095359</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.40024309856525</v>
       </c>
       <c r="E31">
-        <v>-29.74192799685066</v>
+        <v>-30.1722824672216</v>
       </c>
       <c r="F31">
-        <v>4.486274752903032</v>
+        <v>3.897790222902634</v>
       </c>
       <c r="G31">
-        <v>-2.168209846158605</v>
+        <v>-5.228223230654367</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.623276775511211</v>
       </c>
       <c r="E32">
-        <v>-28.48726898828551</v>
+        <v>-28.23629190183241</v>
       </c>
       <c r="F32">
-        <v>4.24414353919741</v>
+        <v>3.854184464226924</v>
       </c>
       <c r="G32">
-        <v>-2.517773660195789</v>
+        <v>-4.870641275321068</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.845841847458397</v>
       </c>
       <c r="E33">
-        <v>-28.63283225678807</v>
+        <v>-29.03557662113424</v>
       </c>
       <c r="F33">
-        <v>4.013299397551125</v>
+        <v>3.129334936377612</v>
       </c>
       <c r="G33">
-        <v>-2.580670714896403</v>
+        <v>-5.066853998888132</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.065574577253484</v>
       </c>
       <c r="E34">
-        <v>-28.32828332282422</v>
+        <v>-28.10088600052906</v>
       </c>
       <c r="F34">
-        <v>3.978663749180465</v>
+        <v>3.273213035089371</v>
       </c>
       <c r="G34">
-        <v>-2.684436454279318</v>
+        <v>-6.036055932056243</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.283522572433511</v>
       </c>
       <c r="E35">
-        <v>-26.85267553895083</v>
+        <v>-27.95943911489947</v>
       </c>
       <c r="F35">
-        <v>4.211669649401324</v>
+        <v>3.098416245790488</v>
       </c>
       <c r="G35">
-        <v>-2.453410033821279</v>
+        <v>-5.537375215293667</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.502648143898595</v>
       </c>
       <c r="E36">
-        <v>-26.31908091815302</v>
+        <v>-27.88492307510326</v>
       </c>
       <c r="F36">
-        <v>4.155882024824054</v>
+        <v>3.723951575682592</v>
       </c>
       <c r="G36">
-        <v>-2.730840371103282</v>
+        <v>-5.653429699718358</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.719077206810033</v>
       </c>
       <c r="E37">
-        <v>-26.59540840210107</v>
+        <v>-27.60725969132295</v>
       </c>
       <c r="F37">
-        <v>4.185853659273746</v>
+        <v>3.115768911505958</v>
       </c>
       <c r="G37">
-        <v>-2.263656184601333</v>
+        <v>-5.510235362962722</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.938634866137066</v>
       </c>
       <c r="E38">
-        <v>-25.51298537394365</v>
+        <v>-27.01969018882772</v>
       </c>
       <c r="F38">
-        <v>4.195610871418769</v>
+        <v>3.399679870966788</v>
       </c>
       <c r="G38">
-        <v>-1.950759972957117</v>
+        <v>-6.035870541506044</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.159553407549682</v>
       </c>
       <c r="E39">
-        <v>-25.60034869449963</v>
+        <v>-25.99141412438002</v>
       </c>
       <c r="F39">
-        <v>3.864866560626563</v>
+        <v>2.925361532998589</v>
       </c>
       <c r="G39">
-        <v>-2.566150662161159</v>
+        <v>-4.597925154886986</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.381239452556271</v>
       </c>
       <c r="E40">
-        <v>-24.0829204531654</v>
+        <v>-25.15374605938917</v>
       </c>
       <c r="F40">
-        <v>4.070390412096802</v>
+        <v>3.624273125364833</v>
       </c>
       <c r="G40">
-        <v>-2.07620316453118</v>
+        <v>-4.890997819842046</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.606706295380542</v>
       </c>
       <c r="E41">
-        <v>-22.88417904164696</v>
+        <v>-26.5118897559776</v>
       </c>
       <c r="F41">
-        <v>4.329939223460427</v>
+        <v>3.142791685541102</v>
       </c>
       <c r="G41">
-        <v>-2.923848486588332</v>
+        <v>-6.302488637056788</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.831700294165855</v>
       </c>
       <c r="E42">
-        <v>-23.44236327630642</v>
+        <v>-23.44351803717838</v>
       </c>
       <c r="F42">
-        <v>4.273469021633602</v>
+        <v>3.431475934631066</v>
       </c>
       <c r="G42">
-        <v>-2.452744614167885</v>
+        <v>-5.22284690469859</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.059359909894932</v>
       </c>
       <c r="E43">
-        <v>-22.75057547299867</v>
+        <v>-23.46020546389664</v>
       </c>
       <c r="F43">
-        <v>4.321060968098474</v>
+        <v>3.588915307096732</v>
       </c>
       <c r="G43">
-        <v>-3.03555622471996</v>
+        <v>-6.054495670709984</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.288189934091593</v>
       </c>
       <c r="E44">
-        <v>-22.21735218706949</v>
+        <v>-23.37556375621928</v>
       </c>
       <c r="F44">
-        <v>4.036030328555428</v>
+        <v>3.259943163223904</v>
       </c>
       <c r="G44">
-        <v>-2.408048938842185</v>
+        <v>-6.365703504129171</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.515302385679496</v>
       </c>
       <c r="E45">
-        <v>-20.48285607265159</v>
+        <v>-22.16661063581354</v>
       </c>
       <c r="F45">
-        <v>4.078065050963022</v>
+        <v>3.33132078883276</v>
       </c>
       <c r="G45">
-        <v>-3.825806618762767</v>
+        <v>-6.576237647699123</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.743867545519032</v>
       </c>
       <c r="E46">
-        <v>-21.38187590349835</v>
+        <v>-22.92361752177976</v>
       </c>
       <c r="F46">
-        <v>3.940922453509627</v>
+        <v>3.385656155085571</v>
       </c>
       <c r="G46">
-        <v>-4.010740313677534</v>
+        <v>-6.226988335488169</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.968458119430818</v>
       </c>
       <c r="E47">
-        <v>-20.65116133762066</v>
+        <v>-22.15666157841869</v>
       </c>
       <c r="F47">
-        <v>4.198399777535857</v>
+        <v>3.093972366991765</v>
       </c>
       <c r="G47">
-        <v>-4.340599760664976</v>
+        <v>-6.701637802181176</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.188428046554078</v>
       </c>
       <c r="E48">
-        <v>-19.72319550091687</v>
+        <v>-21.15888025793864</v>
       </c>
       <c r="F48">
-        <v>4.185319950380243</v>
+        <v>3.073221068381762</v>
       </c>
       <c r="G48">
-        <v>-4.072448882529549</v>
+        <v>-6.389052781817651</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.401727273765136</v>
       </c>
       <c r="E49">
-        <v>-19.14921142044465</v>
+        <v>-19.83931463142155</v>
       </c>
       <c r="F49">
-        <v>3.7677109538321</v>
+        <v>2.952441320446688</v>
       </c>
       <c r="G49">
-        <v>-4.548826453994055</v>
+        <v>-5.838416363361754</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.600806118661296</v>
       </c>
       <c r="E50">
-        <v>-17.34577834620799</v>
+        <v>-19.79094147207162</v>
       </c>
       <c r="F50">
-        <v>3.978180718876255</v>
+        <v>2.866878440953241</v>
       </c>
       <c r="G50">
-        <v>-4.355358172679047</v>
+        <v>-6.742764709415542</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.788072528730734</v>
       </c>
       <c r="E51">
-        <v>-18.16437247867853</v>
+        <v>-19.69194903026395</v>
       </c>
       <c r="F51">
-        <v>4.064549704680662</v>
+        <v>2.881591068907674</v>
       </c>
       <c r="G51">
-        <v>-4.683919885815095</v>
+        <v>-6.173046306471285</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.956157242955674</v>
       </c>
       <c r="E52">
-        <v>-17.69621430729156</v>
+        <v>-19.30736384668853</v>
       </c>
       <c r="F52">
-        <v>4.014466588810804</v>
+        <v>3.254724852232531</v>
       </c>
       <c r="G52">
-        <v>-4.441286692696369</v>
+        <v>-6.687935454194132</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.102879786644149</v>
       </c>
       <c r="E53">
-        <v>-17.84947598160715</v>
+        <v>-18.75133516565673</v>
       </c>
       <c r="F53">
-        <v>3.886054962069228</v>
+        <v>3.315543910503152</v>
       </c>
       <c r="G53">
-        <v>-4.647997156168462</v>
+        <v>-6.669396399174214</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.227466489301975</v>
       </c>
       <c r="E54">
-        <v>-15.85178042938944</v>
+        <v>-18.82784826249032</v>
       </c>
       <c r="F54">
-        <v>3.83795147859367</v>
+        <v>3.150444152524505</v>
       </c>
       <c r="G54">
-        <v>-5.746757289015952</v>
+        <v>-8.189036118065866</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.325190397032465</v>
       </c>
       <c r="E55">
-        <v>-16.184496471681</v>
+        <v>-17.92516489617135</v>
       </c>
       <c r="F55">
-        <v>3.73765538296889</v>
+        <v>3.03613067584217</v>
       </c>
       <c r="G55">
-        <v>-5.710500194269854</v>
+        <v>-7.368159867239262</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.401742379685146</v>
       </c>
       <c r="E56">
-        <v>-14.71107594075331</v>
+        <v>-16.71505701489367</v>
       </c>
       <c r="F56">
-        <v>3.796775124792244</v>
+        <v>3.179463979719017</v>
       </c>
       <c r="G56">
-        <v>-5.216755500906332</v>
+        <v>-7.183918076342202</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.455554973107498</v>
       </c>
       <c r="E57">
-        <v>-15.7376900552402</v>
+        <v>-17.28677685836205</v>
       </c>
       <c r="F57">
-        <v>4.219068723438258</v>
+        <v>3.317712003901388</v>
       </c>
       <c r="G57">
-        <v>-5.228233162290985</v>
+        <v>-7.622512391567007</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.491202608601089</v>
       </c>
       <c r="E58">
-        <v>-14.48268688265046</v>
+        <v>-16.85662616932145</v>
       </c>
       <c r="F58">
-        <v>3.668651732527278</v>
+        <v>3.227302984306697</v>
       </c>
       <c r="G58">
-        <v>-6.263698974973147</v>
+        <v>-8.046997161703437</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.515888922234829</v>
       </c>
       <c r="E59">
-        <v>-14.48807123824558</v>
+        <v>-15.99617988007203</v>
       </c>
       <c r="F59">
-        <v>3.71426721400968</v>
+        <v>3.209923395590664</v>
       </c>
       <c r="G59">
-        <v>-6.123997263761443</v>
+        <v>-8.519577537434399</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.53111175155348</v>
       </c>
       <c r="E60">
-        <v>-14.68987815392341</v>
+        <v>-15.72707531216622</v>
       </c>
       <c r="F60">
-        <v>3.224088061298355</v>
+        <v>2.859560135917995</v>
       </c>
       <c r="G60">
-        <v>-5.906136882913085</v>
+        <v>-8.685892724236304</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.545678528046304</v>
       </c>
       <c r="E61">
-        <v>-14.07094444045105</v>
+        <v>-16.24087144460249</v>
       </c>
       <c r="F61">
-        <v>3.734285256780835</v>
+        <v>3.138553688511386</v>
       </c>
       <c r="G61">
-        <v>-6.172231912268624</v>
+        <v>-8.976426200762743</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.563215683085462</v>
       </c>
       <c r="E62">
-        <v>-14.54905619770688</v>
+        <v>-14.73518553637015</v>
       </c>
       <c r="F62">
-        <v>3.392266543576616</v>
+        <v>3.191997428333805</v>
       </c>
       <c r="G62">
-        <v>-6.006115358199074</v>
+        <v>-8.436310696030649</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.585821789912613</v>
       </c>
       <c r="E63">
-        <v>-13.67524638166082</v>
+        <v>-13.3985837906362</v>
       </c>
       <c r="F63">
-        <v>3.45504306235872</v>
+        <v>3.190947431311869</v>
       </c>
       <c r="G63">
-        <v>-6.700853202888369</v>
+        <v>-7.820188376262428</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.622118266541515</v>
       </c>
       <c r="E64">
-        <v>-13.42720374636468</v>
+        <v>-14.34850366932918</v>
       </c>
       <c r="F64">
-        <v>3.044411874074003</v>
+        <v>3.213342616662098</v>
       </c>
       <c r="G64">
-        <v>-6.868178106079752</v>
+        <v>-8.456687103824864</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.669989579852926</v>
       </c>
       <c r="E65">
-        <v>-13.47611126564752</v>
+        <v>-15.00097526130234</v>
       </c>
       <c r="F65">
-        <v>3.639627154215018</v>
+        <v>2.839801820916973</v>
       </c>
       <c r="G65">
-        <v>-6.1191969727295</v>
+        <v>-8.345562021708147</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.733315544893623</v>
       </c>
       <c r="E66">
-        <v>-13.030061104366</v>
+        <v>-14.45655758762621</v>
       </c>
       <c r="F66">
-        <v>3.049129733996097</v>
+        <v>3.114292897592769</v>
       </c>
       <c r="G66">
-        <v>-7.012736387597568</v>
+        <v>-8.243617082371831</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.813077607764013</v>
       </c>
       <c r="E67">
-        <v>-13.09511263348618</v>
+        <v>-13.71694909879745</v>
       </c>
       <c r="F67">
-        <v>3.533713653708175</v>
+        <v>2.78182393105865</v>
       </c>
       <c r="G67">
-        <v>-6.767554074413605</v>
+        <v>-8.89749948456098</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.90485732716583</v>
       </c>
       <c r="E68">
-        <v>-11.39718847515423</v>
+        <v>-13.93463737282017</v>
       </c>
       <c r="F68">
-        <v>3.607561860545116</v>
+        <v>2.798728408000051</v>
       </c>
       <c r="G68">
-        <v>-7.142095954544589</v>
+        <v>-9.378932259063953</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.01278071609479</v>
       </c>
       <c r="E69">
-        <v>-11.90228088054776</v>
+        <v>-13.97074289608333</v>
       </c>
       <c r="F69">
-        <v>2.962542196775361</v>
+        <v>2.575476552512383</v>
       </c>
       <c r="G69">
-        <v>-6.615186215968648</v>
+        <v>-9.402480169484788</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.12856182297022</v>
       </c>
       <c r="E70">
-        <v>-12.62536043924851</v>
+        <v>-14.7372233496736</v>
       </c>
       <c r="F70">
-        <v>3.159635981657715</v>
+        <v>2.586844393573407</v>
       </c>
       <c r="G70">
-        <v>-7.044355408043147</v>
+        <v>-8.342771231818542</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.2501547465979</v>
       </c>
       <c r="E71">
-        <v>-12.63817602069022</v>
+        <v>-14.98393461361148</v>
       </c>
       <c r="F71">
-        <v>3.103140440536244</v>
+        <v>2.438318117999834</v>
       </c>
       <c r="G71">
-        <v>-7.024555035172766</v>
+        <v>-9.096052763824309</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.3735157635369</v>
       </c>
       <c r="E72">
-        <v>-12.69398946283476</v>
+        <v>-13.21305221054195</v>
       </c>
       <c r="F72">
-        <v>3.222029243608283</v>
+        <v>2.120636213598174</v>
       </c>
       <c r="G72">
-        <v>-6.867002862413311</v>
+        <v>-8.27377946278013</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.48804869814139</v>
       </c>
       <c r="E73">
-        <v>-12.58984361760635</v>
+        <v>-13.535434275148</v>
       </c>
       <c r="F73">
-        <v>3.144679462992305</v>
+        <v>2.262686715683515</v>
       </c>
       <c r="G73">
-        <v>-6.767001213308546</v>
+        <v>-8.501253667874533</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.58976328611985</v>
       </c>
       <c r="E74">
-        <v>-12.99574432833587</v>
+        <v>-15.45465137281278</v>
       </c>
       <c r="F74">
-        <v>2.738422470446032</v>
+        <v>2.422422461726568</v>
       </c>
       <c r="G74">
-        <v>-7.616523614686465</v>
+        <v>-9.895221767549913</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.66648631892125</v>
       </c>
       <c r="E75">
-        <v>-13.27726597197071</v>
+        <v>-13.91919980492803</v>
       </c>
       <c r="F75">
-        <v>3.110805577166971</v>
+        <v>2.310136128615996</v>
       </c>
       <c r="G75">
-        <v>-6.256495227879694</v>
+        <v>-8.165584213465669</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.70971683336404</v>
       </c>
       <c r="E76">
-        <v>-12.88639526647266</v>
+        <v>-15.76083961436741</v>
       </c>
       <c r="F76">
-        <v>2.672169717179538</v>
+        <v>1.937475873359855</v>
       </c>
       <c r="G76">
-        <v>-5.931763815932583</v>
+        <v>-8.698740951474216</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.71441355271463</v>
       </c>
       <c r="E77">
-        <v>-14.99819930673564</v>
+        <v>-15.3386499826323</v>
       </c>
       <c r="F77">
-        <v>2.594341657377097</v>
+        <v>2.704133653670853</v>
       </c>
       <c r="G77">
-        <v>-5.970268771099846</v>
+        <v>-8.554242259776107</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.66960558738578</v>
       </c>
       <c r="E78">
-        <v>-13.91484341293265</v>
+        <v>-15.99913697359904</v>
       </c>
       <c r="F78">
-        <v>2.853725763325516</v>
+        <v>2.366232575846777</v>
       </c>
       <c r="G78">
-        <v>-5.20000082993208</v>
+        <v>-8.359638461341129</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.57345933678338</v>
       </c>
       <c r="E79">
-        <v>-13.88493284211198</v>
+        <v>-14.16294038991687</v>
       </c>
       <c r="F79">
-        <v>2.822463408554742</v>
+        <v>2.566637889798315</v>
       </c>
       <c r="G79">
-        <v>-6.366378855419183</v>
+        <v>-7.723129802142076</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.42041020411842</v>
       </c>
       <c r="E80">
-        <v>-15.4795172235889</v>
+        <v>-15.71276986277599</v>
       </c>
       <c r="F80">
-        <v>2.527881438635681</v>
+        <v>2.722889482827402</v>
       </c>
       <c r="G80">
-        <v>-5.842283080551622</v>
+        <v>-8.068638197893652</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.20928586784368</v>
       </c>
       <c r="E81">
-        <v>-15.0987178442839</v>
+        <v>-16.79497099570703</v>
       </c>
       <c r="F81">
-        <v>2.455463318240382</v>
+        <v>1.921939718329394</v>
       </c>
       <c r="G81">
-        <v>-4.906385235508579</v>
+        <v>-8.900290274450585</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.946443657786183</v>
       </c>
       <c r="E82">
-        <v>-15.4905576432196</v>
+        <v>-18.13207993052983</v>
       </c>
       <c r="F82">
-        <v>2.575766370694908</v>
+        <v>2.014681536737528</v>
       </c>
       <c r="G82">
-        <v>-5.073283078325397</v>
+        <v>-8.352626725888953</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.631343482565091</v>
       </c>
       <c r="E83">
-        <v>-16.21390891036082</v>
+        <v>-18.55360840505982</v>
       </c>
       <c r="F83">
-        <v>2.821364316649427</v>
+        <v>1.924028626431859</v>
       </c>
       <c r="G83">
-        <v>-5.366521270557421</v>
+        <v>-7.119584244877545</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.277107001528178</v>
       </c>
       <c r="E84">
-        <v>-17.39576817077866</v>
+        <v>-18.40313627073294</v>
       </c>
       <c r="F84">
-        <v>2.836438029552579</v>
+        <v>1.756988828706798</v>
       </c>
       <c r="G84">
-        <v>-4.591797335093795</v>
+        <v>-7.401228906631042</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.893323638742048</v>
       </c>
       <c r="E85">
-        <v>-17.97687554086494</v>
+        <v>-20.1957598775133</v>
       </c>
       <c r="F85">
-        <v>2.391546531199161</v>
+        <v>2.191842798968162</v>
       </c>
       <c r="G85">
-        <v>-4.219010044098623</v>
+        <v>-7.72629137313208</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.492526382596006</v>
       </c>
       <c r="E86">
-        <v>-19.70416232466263</v>
+        <v>-20.52074581467377</v>
       </c>
       <c r="F86">
-        <v>2.709852415731504</v>
+        <v>1.999538140774096</v>
       </c>
       <c r="G86">
-        <v>-3.947095075685045</v>
+        <v>-5.709848016798618</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.094496257444559</v>
       </c>
       <c r="E87">
-        <v>-19.84398801659747</v>
+        <v>-21.53553608352662</v>
       </c>
       <c r="F87">
-        <v>2.334062757586455</v>
+        <v>1.732004284184826</v>
       </c>
       <c r="G87">
-        <v>-3.819089521863586</v>
+        <v>-6.688432036025024</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.711129545777601</v>
       </c>
       <c r="E88">
-        <v>-21.02762696730032</v>
+        <v>-23.15755848901602</v>
       </c>
       <c r="F88">
-        <v>2.785263740306985</v>
+        <v>1.808269226248728</v>
       </c>
       <c r="G88">
-        <v>-3.230017669696749</v>
+        <v>-6.686790005437545</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.363237314444977</v>
       </c>
       <c r="E89">
-        <v>-23.48486300486841</v>
+        <v>-26.37287918936414</v>
       </c>
       <c r="F89">
-        <v>2.182191695119474</v>
+        <v>1.543207534593458</v>
       </c>
       <c r="G89">
-        <v>-2.952766101873866</v>
+        <v>-5.835311071645917</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.068239203713777</v>
       </c>
       <c r="E90">
-        <v>-24.07293063950448</v>
+        <v>-24.79934315507488</v>
       </c>
       <c r="F90">
-        <v>2.259691927797419</v>
+        <v>1.542307989633489</v>
       </c>
       <c r="G90">
-        <v>-2.70918278218537</v>
+        <v>-6.081172046665431</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.836771109131683</v>
       </c>
       <c r="E91">
-        <v>-26.36866770853701</v>
+        <v>-29.45623110018074</v>
       </c>
       <c r="F91">
-        <v>2.260591472757388</v>
+        <v>1.704872234441517</v>
       </c>
       <c r="G91">
-        <v>-3.030110377307859</v>
+        <v>-6.064500139329661</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.682699227018832</v>
       </c>
       <c r="E92">
-        <v>-27.72908017060329</v>
+        <v>-29.56948823511258</v>
       </c>
       <c r="F92">
-        <v>2.243489032576558</v>
+        <v>1.094492970160169</v>
       </c>
       <c r="G92">
-        <v>-3.077192955967373</v>
+        <v>-5.247189346048851</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.609475278858302</v>
       </c>
       <c r="E93">
-        <v>-30.09165298751503</v>
+        <v>-30.78426044461817</v>
       </c>
       <c r="F93">
-        <v>1.540272927532149</v>
+        <v>1.230273580526285</v>
       </c>
       <c r="G93">
-        <v>-2.586464169590127</v>
+        <v>-6.524437541646146</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.615627487634582</v>
       </c>
       <c r="E94">
-        <v>-31.85551172739866</v>
+        <v>-32.75605991822302</v>
       </c>
       <c r="F94">
-        <v>1.304940563321509</v>
+        <v>0.8349061498545735</v>
       </c>
       <c r="G94">
-        <v>-3.309990518288923</v>
+        <v>-6.191674746220764</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.701107923417925</v>
       </c>
       <c r="E95">
-        <v>-34.20849776483617</v>
+        <v>-34.14285074138397</v>
       </c>
       <c r="F95">
-        <v>1.355356257433608</v>
+        <v>0.9010322066478321</v>
       </c>
       <c r="G95">
-        <v>-3.818271817115386</v>
+        <v>-6.648914053922743</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.857009194415371</v>
       </c>
       <c r="E96">
-        <v>-36.29112711130473</v>
+        <v>-37.77034182472524</v>
       </c>
       <c r="F96">
-        <v>1.250126917882234</v>
+        <v>0.252717642721005</v>
       </c>
       <c r="G96">
-        <v>-3.391999352387749</v>
+        <v>-5.258455132518991</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.073076921701568</v>
       </c>
       <c r="E97">
-        <v>-37.81525070145931</v>
+        <v>-37.9542250402807</v>
       </c>
       <c r="F97">
-        <v>1.191336586889291</v>
+        <v>0.255737769901748</v>
       </c>
       <c r="G97">
-        <v>-3.629077450091577</v>
+        <v>-7.216834830639176</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.350370335064635</v>
       </c>
       <c r="E98">
-        <v>-40.00422220305</v>
+        <v>-39.52747578070748</v>
       </c>
       <c r="F98">
-        <v>0.7680753439289442</v>
+        <v>0.1463765416169924</v>
       </c>
       <c r="G98">
-        <v>-3.824217556903917</v>
+        <v>-7.02549191956038</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.664825405569706</v>
       </c>
       <c r="E99">
-        <v>-42.43764752428575</v>
+        <v>-42.45859398080823</v>
       </c>
       <c r="F99">
-        <v>0.7279489871494549</v>
+        <v>-0.2971775170908376</v>
       </c>
       <c r="G99">
-        <v>-4.367163578072088</v>
+        <v>-6.565551206698355</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.033706597270283</v>
       </c>
       <c r="E100">
-        <v>-44.43718842966158</v>
+        <v>-44.90972789965097</v>
       </c>
       <c r="F100">
-        <v>0.2268050465325848</v>
+        <v>0.01108529637874676</v>
       </c>
       <c r="G100">
-        <v>-3.518528402898694</v>
+        <v>-6.476798791336034</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.414300710596278</v>
       </c>
       <c r="E101">
-        <v>-45.97011763752407</v>
+        <v>-47.12489662337604</v>
       </c>
       <c r="F101">
-        <v>0.1813574378772189</v>
+        <v>-1.254513489620745</v>
       </c>
       <c r="G101">
-        <v>-4.149703773233981</v>
+        <v>-5.404105894064767</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.856250377902731</v>
       </c>
       <c r="E102">
-        <v>-48.0833028623594</v>
+        <v>-48.90364498579689</v>
       </c>
       <c r="F102">
-        <v>-0.3243056075693577</v>
+        <v>-1.120330838523307</v>
       </c>
       <c r="G102">
-        <v>-3.855608149707286</v>
+        <v>-7.680446938504252</v>
       </c>
     </row>
   </sheetData>
